--- a/backend/data/financials_by_company/1119.HK.xlsx
+++ b/backend/data/financials_by_company/1119.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,626 +682,682 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-19241227.659171</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.051406</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-21904000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-374300000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-374300000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-528827000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>73699000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1086855000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-396204000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-469903000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-100353000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>104214000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3861000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-173768227.659171</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-528827000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1562593000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>-345360000</v>
-      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>1625076000</v>
+        <v>1259699000</v>
       </c>
       <c r="U2" t="n">
-        <v>1625076000</v>
+        <v>1259699000</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.33</v>
+        <v>-0.13</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-528827000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-528827000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-528827000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15777000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-544604000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-544604000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-29513000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-574117000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-27607000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-292900000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-8303000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>291231000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>9972000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-100353000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>104214000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>3861000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-48949000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>475738000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>165164000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>322983000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>196485000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>126498000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>426789000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1086855000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1513644000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1513644000</v>
-      </c>
+        <v>-0.13</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>-13913000</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-12465562.589693</v>
+        <v>-313294250</v>
       </c>
       <c r="C3" t="n">
-        <v>0.028759</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>223982000</v>
+        <v>-948158000</v>
       </c>
       <c r="E3" t="n">
-        <v>-433449000</v>
+        <v>-1179955000</v>
       </c>
       <c r="F3" t="n">
-        <v>-433449000</v>
+        <v>-1253177000</v>
       </c>
       <c r="G3" t="n">
-        <v>-452359000</v>
+        <v>-2423954000</v>
       </c>
       <c r="H3" t="n">
-        <v>117767000</v>
+        <v>250839000</v>
       </c>
       <c r="I3" t="n">
-        <v>1243012000</v>
+        <v>2194068000</v>
       </c>
       <c r="J3" t="n">
-        <v>-209467000</v>
+        <v>-2128113000</v>
       </c>
       <c r="K3" t="n">
-        <v>-327234000</v>
+        <v>-2378952000</v>
       </c>
       <c r="L3" t="n">
-        <v>-136918000</v>
+        <v>-120023000</v>
       </c>
       <c r="M3" t="n">
-        <v>143123000</v>
+        <v>128798000</v>
       </c>
       <c r="N3" t="n">
-        <v>6205000</v>
+        <v>8775000</v>
       </c>
       <c r="O3" t="n">
-        <v>-31375562.589693</v>
+        <v>-1410849250</v>
       </c>
       <c r="P3" t="n">
-        <v>-556347000</v>
+        <v>-2492293000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1800560000</v>
+        <v>3658930000</v>
       </c>
       <c r="R3" t="n">
-        <v>3307000</v>
+        <v>4037000</v>
       </c>
       <c r="S3" t="n">
-        <v>-175291000</v>
+        <v>-2318748000</v>
       </c>
       <c r="T3" t="n">
-        <v>1410398000</v>
+        <v>1386326000</v>
       </c>
       <c r="U3" t="n">
-        <v>1410398000</v>
+        <v>1386326000</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.39</v>
+        <v>-1.8</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.39</v>
+        <v>-1.8</v>
       </c>
       <c r="X3" t="n">
-        <v>-556347000</v>
+        <v>-2492293000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-556347000</v>
+        <v>-2492293000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-556347000</v>
+        <v>-2492293000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4471000</v>
+        <v>97624000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-560818000</v>
+        <v>-2589917000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-103988000</v>
+        <v>-68339000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-456830000</v>
+        <v>-2521578000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-13527000</v>
+        <v>13828000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-470357000</v>
+        <v>-2507750000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-11025000</v>
+        <v>-1898000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-405593000</v>
+        <v>-1170027000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>130666000</v>
+        <v>-23212000</v>
       </c>
       <c r="AK3" t="n">
-        <v>251682000</v>
+        <v>367724000</v>
       </c>
       <c r="AL3" t="n">
-        <v>23245000</v>
+        <v>752293000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-136918000</v>
+        <v>-120023000</v>
       </c>
       <c r="AN3" t="n">
-        <v>143123000</v>
+        <v>128798000</v>
       </c>
       <c r="AO3" t="n">
-        <v>6205000</v>
+        <v>8775000</v>
       </c>
       <c r="AP3" t="n">
-        <v>115913000</v>
+        <v>-1064402000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>557548000</v>
+        <v>1464862000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-5661000</v>
+        <v>-15634000</v>
       </c>
       <c r="AS3" t="n">
-        <v>239953000</v>
+        <v>315981000</v>
       </c>
       <c r="AT3" t="n">
-        <v>339708000</v>
+        <v>1182985000</v>
       </c>
       <c r="AU3" t="n">
-        <v>230597000</v>
+        <v>1074799000</v>
       </c>
       <c r="AV3" t="n">
-        <v>109111000</v>
+        <v>108186000</v>
       </c>
       <c r="AW3" t="n">
-        <v>673461000</v>
+        <v>400460000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1243012000</v>
+        <v>2194068000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1916473000</v>
+        <v>2594528000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1916473000</v>
+        <v>2594528000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-313294250</v>
+        <v>-12465562.589693</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25</v>
+        <v>0.028759</v>
       </c>
       <c r="D4" t="n">
-        <v>-948158000</v>
+        <v>223982000</v>
       </c>
       <c r="E4" t="n">
-        <v>-1179955000</v>
+        <v>-433449000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1253177000</v>
+        <v>-433449000</v>
       </c>
       <c r="G4" t="n">
-        <v>-2423954000</v>
+        <v>-452359000</v>
       </c>
       <c r="H4" t="n">
-        <v>250839000</v>
+        <v>117767000</v>
       </c>
       <c r="I4" t="n">
-        <v>2194068000</v>
+        <v>1243012000</v>
       </c>
       <c r="J4" t="n">
-        <v>-2128113000</v>
+        <v>-209467000</v>
       </c>
       <c r="K4" t="n">
-        <v>-2378952000</v>
+        <v>-327234000</v>
       </c>
       <c r="L4" t="n">
-        <v>-120023000</v>
+        <v>-136918000</v>
       </c>
       <c r="M4" t="n">
-        <v>128798000</v>
+        <v>143123000</v>
       </c>
       <c r="N4" t="n">
-        <v>8775000</v>
+        <v>6205000</v>
       </c>
       <c r="O4" t="n">
-        <v>-1410849250</v>
+        <v>-31375562.589693</v>
       </c>
       <c r="P4" t="n">
-        <v>-2492293000</v>
+        <v>-556347000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3658930000</v>
+        <v>1800560000</v>
       </c>
       <c r="R4" t="n">
-        <v>4037000</v>
+        <v>3307000</v>
       </c>
       <c r="S4" t="n">
-        <v>-2318748000</v>
+        <v>-175291000</v>
       </c>
       <c r="T4" t="n">
-        <v>1386326000</v>
+        <v>1410398000</v>
       </c>
       <c r="U4" t="n">
-        <v>1386326000</v>
+        <v>1410398000</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8</v>
+        <v>-0.39</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.8</v>
+        <v>-0.39</v>
       </c>
       <c r="X4" t="n">
-        <v>-2492293000</v>
+        <v>-556347000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2492293000</v>
+        <v>-556347000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2492293000</v>
+        <v>-556347000</v>
       </c>
       <c r="AB4" t="n">
-        <v>97624000</v>
+        <v>4471000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2589917000</v>
+        <v>-560818000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-68339000</v>
+        <v>-103988000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2521578000</v>
+        <v>-456830000</v>
       </c>
       <c r="AF4" t="n">
-        <v>13828000</v>
+        <v>-13527000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2507750000</v>
+        <v>-470357000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1898000</v>
+        <v>-11025000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1170027000</v>
+        <v>-405593000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-23212000</v>
+        <v>130666000</v>
       </c>
       <c r="AK4" t="n">
-        <v>367724000</v>
+        <v>251682000</v>
       </c>
       <c r="AL4" t="n">
-        <v>752293000</v>
+        <v>23245000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-120023000</v>
+        <v>-136918000</v>
       </c>
       <c r="AN4" t="n">
-        <v>128798000</v>
+        <v>143123000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8775000</v>
+        <v>6205000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1064402000</v>
+        <v>115913000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1464862000</v>
+        <v>557548000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-15634000</v>
+        <v>-5661000</v>
       </c>
       <c r="AS4" t="n">
-        <v>315981000</v>
+        <v>239953000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1182985000</v>
+        <v>339708000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1074799000</v>
+        <v>230597000</v>
       </c>
       <c r="AV4" t="n">
-        <v>108186000</v>
+        <v>109111000</v>
       </c>
       <c r="AW4" t="n">
-        <v>400460000</v>
+        <v>673461000</v>
       </c>
       <c r="AX4" t="n">
-        <v>2194068000</v>
+        <v>1243012000</v>
       </c>
       <c r="AY4" t="n">
-        <v>2594528000</v>
+        <v>1916473000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2594528000</v>
+        <v>1916473000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-12643535.434375</v>
+        <v>-19241227.659171</v>
       </c>
       <c r="C5" t="n">
-        <v>0.139364</v>
+        <v>0.051406</v>
       </c>
       <c r="D5" t="n">
-        <v>277294000</v>
+        <v>-21904000</v>
       </c>
       <c r="E5" t="n">
-        <v>-90723000</v>
+        <v>-374300000</v>
       </c>
       <c r="F5" t="n">
-        <v>-90723000</v>
+        <v>-374300000</v>
       </c>
       <c r="G5" t="n">
-        <v>-157478000</v>
+        <v>-528827000</v>
       </c>
       <c r="H5" t="n">
-        <v>233335000</v>
+        <v>73699000</v>
       </c>
       <c r="I5" t="n">
-        <v>1534296000</v>
+        <v>1086855000</v>
       </c>
       <c r="J5" t="n">
-        <v>186571000</v>
+        <v>-396204000</v>
       </c>
       <c r="K5" t="n">
-        <v>-46764000</v>
+        <v>-469903000</v>
       </c>
       <c r="L5" t="n">
-        <v>-129171000</v>
+        <v>-100353000</v>
       </c>
       <c r="M5" t="n">
-        <v>134416000</v>
+        <v>104214000</v>
       </c>
       <c r="N5" t="n">
-        <v>5245000</v>
+        <v>3861000</v>
       </c>
       <c r="O5" t="n">
-        <v>-79398535.434375</v>
+        <v>-173768227.659171</v>
       </c>
       <c r="P5" t="n">
-        <v>-157478000</v>
+        <v>-528827000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2567378000</v>
+        <v>1562593000</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-16584000</v>
+        <v>-345360000</v>
       </c>
       <c r="T5" t="n">
-        <v>1259699000</v>
+        <v>1625076000</v>
       </c>
       <c r="U5" t="n">
-        <v>1259699000</v>
+        <v>1625076000</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.13</v>
+        <v>-0.33</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.13</v>
+        <v>-0.33</v>
       </c>
       <c r="X5" t="n">
-        <v>-157478000</v>
+        <v>-528827000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-157478000</v>
+        <v>-528827000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-157478000</v>
+        <v>-528827000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1548000</v>
+        <v>15777000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-155930000</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>-544604000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
       <c r="AE5" t="n">
-        <v>-155930000</v>
+        <v>-544604000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-25250000</v>
+        <v>-29513000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-181180000</v>
+        <v>-574117000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-81791000</v>
+        <v>-27607000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-88820000</v>
+        <v>-292900000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-2152000</v>
+        <v>-8303000</v>
       </c>
       <c r="AK5" t="n">
-        <v>41299000</v>
+        <v>291231000</v>
       </c>
       <c r="AL5" t="n">
-        <v>49673000</v>
+        <v>9972000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-129171000</v>
+        <v>-100353000</v>
       </c>
       <c r="AN5" t="n">
-        <v>134416000</v>
+        <v>104214000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5245000</v>
+        <v>3861000</v>
       </c>
       <c r="AP5" t="n">
-        <v>70259000</v>
+        <v>-48949000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1033082000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-13913000</v>
-      </c>
+        <v>475738000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>325201000</v>
+        <v>165164000</v>
       </c>
       <c r="AT5" t="n">
-        <v>759807000</v>
+        <v>322983000</v>
       </c>
       <c r="AU5" t="n">
-        <v>509687000</v>
+        <v>196485000</v>
       </c>
       <c r="AV5" t="n">
-        <v>250120000</v>
+        <v>126498000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1103341000</v>
+        <v>426789000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1534296000</v>
+        <v>1086855000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2637637000</v>
+        <v>1513644000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2637637000</v>
+        <v>1513644000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-13995215.680332</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.137712</v>
+      </c>
+      <c r="D6" t="n">
+        <v>264117000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-101627000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-101627000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15940000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>67921000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>805693000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>162490000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>94569000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-68626000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>71470000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2844000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>103571784.319668</v>
+      </c>
+      <c r="P6" t="n">
+        <v>15940000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1200330000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>21669000</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>15940000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>15940000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>15940000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-3978000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>19918000</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>19918000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3181000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>23099000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-21808000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-73718000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-1078000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>73160000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1636000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-68626000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>71470000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2844000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>137759000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>394637000</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>82944000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>326625000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>232152000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>94473000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>532396000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>805693000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1338089000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1338089000</v>
       </c>
     </row>
   </sheetData>
@@ -1315,7 +1371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR5"/>
+  <dimension ref="A1:BR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1667,818 +1723,898 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2533200</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1684783945</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1687317145</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1148757000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1353436000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>215635000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2719338000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-168878000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>215635000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7753000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1373655000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1772592000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1455368000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>81713000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1373655000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-3565735000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3968136000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3968136000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2134852000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>398937000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>398937000</v>
-      </c>
-      <c r="W2" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>73222000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
         <v>0</v>
       </c>
-      <c r="X2" t="n">
-        <v>398937000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1735915000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12286000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>954499000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>7753000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>946746000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>529099000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>117261000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>33073000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>378765000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>3590220000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2023183000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>121960000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>113000000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>296661000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>296661000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>187755000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>37969000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>149786000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6075000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1158020000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1158020000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>139712000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-33688000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>173400000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>127661000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>14652000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>23398000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7689000</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1567037000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>49143000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>65179000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="n">
-        <v>1070195000</v>
-      </c>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="n">
-        <v>158414000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>-164378000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>322792000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>224106000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>27180000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>196926000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>196916000</v>
-      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="n">
+        <v>1621683000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>11331000</v>
+      </c>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="n">
+        <v>37186000</v>
+      </c>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="inlineStr"/>
+        <v>44926</v>
+      </c>
+      <c r="B3" t="n">
+        <v>19021398</v>
+      </c>
       <c r="C3" t="n">
-        <v>1573444745</v>
+        <v>1392314547</v>
       </c>
       <c r="D3" t="n">
-        <v>1573444745</v>
+        <v>1411335945</v>
       </c>
       <c r="E3" t="n">
-        <v>1013292000</v>
+        <v>1412975000</v>
       </c>
       <c r="F3" t="n">
-        <v>1226529000</v>
+        <v>1620541000</v>
       </c>
       <c r="G3" t="n">
-        <v>605131000</v>
+        <v>537564000</v>
       </c>
       <c r="H3" t="n">
-        <v>2849458000</v>
+        <v>3123848000</v>
       </c>
       <c r="I3" t="n">
-        <v>108014000</v>
+        <v>-329469000</v>
       </c>
       <c r="J3" t="n">
-        <v>605131000</v>
+        <v>537564000</v>
       </c>
       <c r="K3" t="n">
-        <v>22808000</v>
+        <v>117039000</v>
       </c>
       <c r="L3" t="n">
-        <v>1645737000</v>
+        <v>1620346000</v>
       </c>
       <c r="M3" t="n">
-        <v>2006560000</v>
+        <v>1620346000</v>
       </c>
       <c r="N3" t="n">
-        <v>1743227000</v>
+        <v>1794542000</v>
       </c>
       <c r="O3" t="n">
-        <v>97490000</v>
+        <v>174196000</v>
       </c>
       <c r="P3" t="n">
-        <v>1645737000</v>
+        <v>1620346000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3036252000</v>
+        <v>-2472523000</v>
       </c>
       <c r="R3" t="n">
-        <v>3745616000</v>
+        <v>3291884000</v>
       </c>
       <c r="S3" t="n">
-        <v>3745616000</v>
+        <v>3291884000</v>
       </c>
       <c r="T3" t="n">
-        <v>1964446000</v>
+        <v>2529176000</v>
       </c>
       <c r="U3" t="n">
-        <v>370362000</v>
+        <v>82113000</v>
       </c>
       <c r="V3" t="n">
-        <v>370362000</v>
+        <v>82113000</v>
       </c>
       <c r="W3" t="n">
-        <v>9539000</v>
+        <v>82113000</v>
       </c>
       <c r="X3" t="n">
-        <v>360823000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1594084000</v>
+        <v>2447063000</v>
       </c>
       <c r="Z3" t="n">
-        <v>11794000</v>
+        <v>5362000</v>
       </c>
       <c r="AA3" t="n">
-        <v>856167000</v>
+        <v>1538428000</v>
       </c>
       <c r="AB3" t="n">
-        <v>13269000</v>
+        <v>34926000</v>
       </c>
       <c r="AC3" t="n">
-        <v>842898000</v>
+        <v>1503502000</v>
       </c>
       <c r="AD3" t="n">
-        <v>444661000</v>
+        <v>679138000</v>
       </c>
       <c r="AE3" t="n">
-        <v>102344000</v>
+        <v>157893000</v>
       </c>
       <c r="AF3" t="n">
-        <v>68902000</v>
+        <v>77747000</v>
       </c>
       <c r="AG3" t="n">
-        <v>273415000</v>
+        <v>443498000</v>
       </c>
       <c r="AH3" t="n">
-        <v>3707673000</v>
+        <v>4323718000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2005575000</v>
+        <v>2206124000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>72620000</v>
+        <v>91182000</v>
       </c>
       <c r="AK3" t="n">
-        <v>110539000</v>
+        <v>113553000</v>
       </c>
       <c r="AL3" t="n">
-        <v>325743000</v>
+        <v>348897000</v>
       </c>
       <c r="AM3" t="n">
-        <v>325743000</v>
+        <v>348897000</v>
       </c>
       <c r="AN3" t="n">
-        <v>330033000</v>
+        <v>347461000</v>
       </c>
       <c r="AO3" t="n">
-        <v>54628000</v>
+        <v>79060000</v>
       </c>
       <c r="AP3" t="n">
-        <v>275405000</v>
+        <v>268401000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6515000</v>
+        <v>6955000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1040606000</v>
+        <v>1082782000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1040606000</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+        <v>1082782000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
       <c r="AU3" t="n">
-        <v>119519000</v>
+        <v>215294000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-33310000</v>
+        <v>-58530000</v>
       </c>
       <c r="AW3" t="n">
-        <v>152829000</v>
+        <v>273824000</v>
       </c>
       <c r="AX3" t="n">
-        <v>94263000</v>
+        <v>72164000</v>
       </c>
       <c r="AY3" t="n">
-        <v>14423000</v>
+        <v>16195000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22083000</v>
+        <v>24809000</v>
       </c>
       <c r="BA3" t="n">
-        <v>22060000</v>
+        <v>160656000</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>1702098000</v>
+        <v>2117594000</v>
       </c>
       <c r="BE3" t="n">
-        <v>47288000</v>
+        <v>55405000</v>
       </c>
       <c r="BF3" t="n">
-        <v>38105000</v>
+        <v>87099000</v>
       </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>20688000</v>
       </c>
       <c r="BI3" t="n">
-        <v>983871000</v>
+        <v>1013086000</v>
       </c>
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>369260000</v>
+        <v>724932000</v>
       </c>
       <c r="BL3" t="n">
-        <v>-177141000</v>
+        <v>-149993000</v>
       </c>
       <c r="BM3" t="n">
-        <v>546401000</v>
+        <v>874925000</v>
       </c>
       <c r="BN3" t="n">
-        <v>263574000</v>
+        <v>216384000</v>
       </c>
       <c r="BO3" t="n">
-        <v>73145000</v>
+        <v>125857000</v>
       </c>
       <c r="BP3" t="n">
-        <v>190429000</v>
+        <v>90527000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="BR3" t="n">
-        <v>190419000</v>
+        <v>90502000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="n">
-        <v>19021398</v>
-      </c>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1392314547</v>
+        <v>1573444745</v>
       </c>
       <c r="D4" t="n">
-        <v>1411335945</v>
+        <v>1573444745</v>
       </c>
       <c r="E4" t="n">
-        <v>1412975000</v>
+        <v>1013292000</v>
       </c>
       <c r="F4" t="n">
-        <v>1620541000</v>
+        <v>1226529000</v>
       </c>
       <c r="G4" t="n">
-        <v>537564000</v>
+        <v>605131000</v>
       </c>
       <c r="H4" t="n">
-        <v>3123848000</v>
+        <v>2849458000</v>
       </c>
       <c r="I4" t="n">
-        <v>-329469000</v>
+        <v>108014000</v>
       </c>
       <c r="J4" t="n">
-        <v>537564000</v>
+        <v>605131000</v>
       </c>
       <c r="K4" t="n">
-        <v>117039000</v>
+        <v>22808000</v>
       </c>
       <c r="L4" t="n">
-        <v>1620346000</v>
+        <v>1645737000</v>
       </c>
       <c r="M4" t="n">
-        <v>1620346000</v>
+        <v>2006560000</v>
       </c>
       <c r="N4" t="n">
-        <v>1794542000</v>
+        <v>1743227000</v>
       </c>
       <c r="O4" t="n">
-        <v>174196000</v>
+        <v>97490000</v>
       </c>
       <c r="P4" t="n">
-        <v>1620346000</v>
+        <v>1645737000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2472523000</v>
+        <v>-3036252000</v>
       </c>
       <c r="R4" t="n">
-        <v>3291884000</v>
+        <v>3745616000</v>
       </c>
       <c r="S4" t="n">
-        <v>3291884000</v>
+        <v>3745616000</v>
       </c>
       <c r="T4" t="n">
-        <v>2529176000</v>
+        <v>1964446000</v>
       </c>
       <c r="U4" t="n">
-        <v>82113000</v>
+        <v>370362000</v>
       </c>
       <c r="V4" t="n">
-        <v>82113000</v>
+        <v>370362000</v>
       </c>
       <c r="W4" t="n">
-        <v>82113000</v>
+        <v>9539000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>360823000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2447063000</v>
+        <v>1594084000</v>
       </c>
       <c r="Z4" t="n">
-        <v>5362000</v>
+        <v>11794000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1538428000</v>
+        <v>856167000</v>
       </c>
       <c r="AB4" t="n">
-        <v>34926000</v>
+        <v>13269000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1503502000</v>
+        <v>842898000</v>
       </c>
       <c r="AD4" t="n">
-        <v>679138000</v>
+        <v>444661000</v>
       </c>
       <c r="AE4" t="n">
-        <v>157893000</v>
+        <v>102344000</v>
       </c>
       <c r="AF4" t="n">
-        <v>77747000</v>
+        <v>68902000</v>
       </c>
       <c r="AG4" t="n">
-        <v>443498000</v>
+        <v>273415000</v>
       </c>
       <c r="AH4" t="n">
-        <v>4323718000</v>
+        <v>3707673000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2206124000</v>
+        <v>2005575000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91182000</v>
+        <v>72620000</v>
       </c>
       <c r="AK4" t="n">
-        <v>113553000</v>
+        <v>110539000</v>
       </c>
       <c r="AL4" t="n">
-        <v>348897000</v>
+        <v>325743000</v>
       </c>
       <c r="AM4" t="n">
-        <v>348897000</v>
+        <v>325743000</v>
       </c>
       <c r="AN4" t="n">
-        <v>347461000</v>
+        <v>330033000</v>
       </c>
       <c r="AO4" t="n">
-        <v>79060000</v>
+        <v>54628000</v>
       </c>
       <c r="AP4" t="n">
-        <v>268401000</v>
+        <v>275405000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6955000</v>
+        <v>6515000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1082782000</v>
+        <v>1040606000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1082782000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
+        <v>1040606000</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>215294000</v>
+        <v>119519000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-58530000</v>
+        <v>-33310000</v>
       </c>
       <c r="AW4" t="n">
-        <v>273824000</v>
+        <v>152829000</v>
       </c>
       <c r="AX4" t="n">
-        <v>72164000</v>
+        <v>94263000</v>
       </c>
       <c r="AY4" t="n">
-        <v>16195000</v>
+        <v>14423000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>24809000</v>
+        <v>22083000</v>
       </c>
       <c r="BA4" t="n">
-        <v>160656000</v>
+        <v>22060000</v>
       </c>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>2117594000</v>
+        <v>1702098000</v>
       </c>
       <c r="BE4" t="n">
-        <v>55405000</v>
+        <v>47288000</v>
       </c>
       <c r="BF4" t="n">
-        <v>87099000</v>
+        <v>38105000</v>
       </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>20688000</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>1013086000</v>
+        <v>983871000</v>
       </c>
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="n">
-        <v>724932000</v>
+        <v>369260000</v>
       </c>
       <c r="BL4" t="n">
-        <v>-149993000</v>
+        <v>-177141000</v>
       </c>
       <c r="BM4" t="n">
-        <v>874925000</v>
+        <v>546401000</v>
       </c>
       <c r="BN4" t="n">
-        <v>216384000</v>
+        <v>263574000</v>
       </c>
       <c r="BO4" t="n">
-        <v>125857000</v>
+        <v>73145000</v>
       </c>
       <c r="BP4" t="n">
-        <v>90527000</v>
+        <v>190429000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="BR4" t="n">
-        <v>90502000</v>
+        <v>190419000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2533200</v>
+      </c>
       <c r="C5" t="n">
-        <v>1387475615</v>
+        <v>1684783945</v>
       </c>
       <c r="D5" t="n">
-        <v>1387475615</v>
+        <v>1687317145</v>
       </c>
       <c r="E5" t="n">
-        <v>1037090000</v>
+        <v>1149696000</v>
       </c>
       <c r="F5" t="n">
-        <v>1831717000</v>
+        <v>1354375000</v>
       </c>
       <c r="G5" t="n">
-        <v>2086642000</v>
+        <v>215635000</v>
       </c>
       <c r="H5" t="n">
-        <v>5686941000</v>
+        <v>2720277000</v>
       </c>
       <c r="I5" t="n">
-        <v>2116949000</v>
+        <v>-168878000</v>
       </c>
       <c r="J5" t="n">
-        <v>2086642000</v>
+        <v>215635000</v>
       </c>
       <c r="K5" t="n">
-        <v>79826000</v>
+        <v>7753000</v>
       </c>
       <c r="L5" t="n">
-        <v>3935050000</v>
+        <v>1373655000</v>
       </c>
       <c r="M5" t="n">
-        <v>4787230000</v>
+        <v>1772592000</v>
       </c>
       <c r="N5" t="n">
-        <v>4209242000</v>
+        <v>1455368000</v>
       </c>
       <c r="O5" t="n">
-        <v>274192000</v>
+        <v>81713000</v>
       </c>
       <c r="P5" t="n">
-        <v>3935050000</v>
+        <v>1373655000</v>
       </c>
       <c r="Q5" t="n">
-        <v>24055000</v>
+        <v>-3565735000</v>
       </c>
       <c r="R5" t="n">
-        <v>3166013000</v>
+        <v>3968136000</v>
       </c>
       <c r="S5" t="n">
-        <v>3166013000</v>
+        <v>3968136000</v>
       </c>
       <c r="T5" t="n">
-        <v>2401698000</v>
+        <v>2134852000</v>
       </c>
       <c r="U5" t="n">
-        <v>912125000</v>
+        <v>398937000</v>
       </c>
       <c r="V5" t="n">
-        <v>912125000</v>
+        <v>398937000</v>
       </c>
       <c r="W5" t="n">
-        <v>59945000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>852180000</v>
+        <v>398937000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1489573000</v>
+        <v>1735915000</v>
       </c>
       <c r="Z5" t="n">
-        <v>2538000</v>
+        <v>12286000</v>
       </c>
       <c r="AA5" t="n">
-        <v>919592000</v>
+        <v>955438000</v>
       </c>
       <c r="AB5" t="n">
-        <v>19881000</v>
+        <v>7753000</v>
       </c>
       <c r="AC5" t="n">
-        <v>899711000</v>
+        <v>947685000</v>
       </c>
       <c r="AD5" t="n">
-        <v>305009000</v>
+        <v>533793000</v>
       </c>
       <c r="AE5" t="n">
-        <v>126665000</v>
+        <v>121955000</v>
       </c>
       <c r="AF5" t="n">
-        <v>65844000</v>
+        <v>33073000</v>
       </c>
       <c r="AG5" t="n">
-        <v>112500000</v>
+        <v>378765000</v>
       </c>
       <c r="AH5" t="n">
-        <v>6610940000</v>
+        <v>3590220000</v>
       </c>
       <c r="AI5" t="n">
-        <v>3004418000</v>
+        <v>2023183000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>31152000</v>
+        <v>121960000</v>
       </c>
       <c r="AK5" t="n">
-        <v>125572000</v>
+        <v>113000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>457507000</v>
+        <v>296661000</v>
       </c>
       <c r="AM5" t="n">
-        <v>457507000</v>
+        <v>296661000</v>
       </c>
       <c r="AN5" t="n">
-        <v>372185000</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+        <v>187755000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>37969000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>149786000</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>31860000</v>
+        <v>6075000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1848408000</v>
+        <v>1158020000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1775186000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>73222000</v>
-      </c>
+        <v>1158020000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>137575000</v>
+        <v>139712000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-58222000</v>
+        <v>-33688000</v>
       </c>
       <c r="AW5" t="n">
-        <v>195797000</v>
+        <v>173400000</v>
       </c>
       <c r="AX5" t="n">
-        <v>43935000</v>
+        <v>127661000</v>
       </c>
       <c r="AY5" t="n">
-        <v>21110000</v>
+        <v>14652000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>23573000</v>
+        <v>23493000</v>
       </c>
       <c r="BA5" t="n">
-        <v>107179000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
+        <v>7594000</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3606522000</v>
+        <v>1567037000</v>
       </c>
       <c r="BE5" t="n">
-        <v>91296000</v>
+        <v>49143000</v>
       </c>
       <c r="BF5" t="n">
-        <v>10246000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1621683000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>11331000</v>
-      </c>
+        <v>65179000</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="n">
-        <v>1923543000</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>37186000</v>
-      </c>
+        <v>1070195000</v>
+      </c>
+      <c r="BJ5" t="inlineStr"/>
       <c r="BK5" t="n">
-        <v>781346000</v>
+        <v>158414000</v>
       </c>
       <c r="BL5" t="n">
-        <v>-87087000</v>
+        <v>-164378000</v>
       </c>
       <c r="BM5" t="n">
-        <v>868433000</v>
+        <v>322792000</v>
       </c>
       <c r="BN5" t="n">
-        <v>788760000</v>
+        <v>224106000</v>
       </c>
       <c r="BO5" t="n">
-        <v>73959000</v>
+        <v>27180000</v>
       </c>
       <c r="BP5" t="n">
-        <v>714801000</v>
+        <v>196926000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1181000</v>
+        <v>10000</v>
       </c>
       <c r="BR5" t="n">
-        <v>713620000</v>
+        <v>196916000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>23390000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2041015665</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2064405665</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1123065000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1322504000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>386632000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2985411000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-56310000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>386632000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11532000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1674439000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2088960000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1760130000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>85691000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1674439000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-3551622000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4258522000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4258522000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1864612000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>421775000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>421775000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>7254000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>414521000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1442837000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>12409000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>900729000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4278000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>896451000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>326780000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>114973000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>32990000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>178817000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3624742000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2238215000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>150169000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>111823000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>273841000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>273841000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>223134000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>43313000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>179821000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5635000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1287807000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1287807000</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>185806000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-34685000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>220491000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>170131000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>15254000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>23658000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>11448000</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1386527000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>16849000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>31879000</v>
+      </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="n">
+        <v>931426000</v>
+      </c>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="n">
+        <v>207037000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-13428000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>220465000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>199336000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>11429000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>187907000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>14000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>187893000</v>
       </c>
     </row>
   </sheetData>
@@ -2492,7 +2628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD5"/>
+  <dimension ref="A1:BD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2774,666 +2910,728 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-119312000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-10051000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-1080341000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1188738000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>232571000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-270988000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>196926000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>190429000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-55000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6552000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>217060000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-27667000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-73481000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>222520000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-10051000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>232571000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>108397000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>108397000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-1080341000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1188738000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-362184000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-2155000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>845000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-3000000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>22500000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>22500000</v>
-      </c>
+      <c r="X2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-255777000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>-255777000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-15211000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-15211000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>151676000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-3273000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-63984000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-201000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-64544000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>168956000</v>
-      </c>
+        <v>-117290000</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>21300000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-168195000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>272202000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>15569000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-29513000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>73699000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>59983000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>13716000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>81400000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5811000</v>
-      </c>
+        <v>-11331000</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-6669000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-544604000</v>
-      </c>
+        <v>4806000</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>123102000</v>
+        <v>-127966000</v>
       </c>
       <c r="C3" t="n">
-        <v>-3184000</v>
+        <v>-33191000</v>
       </c>
       <c r="D3" t="n">
-        <v>-2022209000</v>
+        <v>-1002816000</v>
       </c>
       <c r="E3" t="n">
-        <v>1602662000</v>
+        <v>636700000</v>
       </c>
       <c r="F3" t="n">
-        <v>456916000</v>
+        <v>159062000</v>
       </c>
       <c r="G3" t="n">
-        <v>-129858000</v>
+        <v>-221887000</v>
       </c>
       <c r="H3" t="n">
-        <v>190429000</v>
+        <v>90527000</v>
       </c>
       <c r="I3" t="n">
-        <v>90527000</v>
+        <v>714801000</v>
       </c>
       <c r="J3" t="n">
-        <v>2982000</v>
+        <v>9651000</v>
       </c>
       <c r="K3" t="n">
-        <v>96920000</v>
+        <v>-633925000</v>
       </c>
       <c r="L3" t="n">
-        <v>-18115000</v>
+        <v>-406158000</v>
       </c>
       <c r="M3" t="n">
-        <v>38050000</v>
+        <v>-57231000</v>
       </c>
       <c r="N3" t="n">
-        <v>-77542000</v>
+        <v>-78164000</v>
       </c>
       <c r="O3" t="n">
-        <v>453732000</v>
+        <v>125871000</v>
       </c>
       <c r="P3" t="n">
-        <v>-3184000</v>
+        <v>-33191000</v>
       </c>
       <c r="Q3" t="n">
-        <v>456916000</v>
+        <v>159062000</v>
       </c>
       <c r="R3" t="n">
-        <v>-419547000</v>
+        <v>-366116000</v>
       </c>
       <c r="S3" t="n">
-        <v>-419547000</v>
+        <v>-366116000</v>
       </c>
       <c r="T3" t="n">
-        <v>-2022209000</v>
+        <v>-1002816000</v>
       </c>
       <c r="U3" t="n">
-        <v>1602662000</v>
+        <v>636700000</v>
       </c>
       <c r="V3" t="n">
-        <v>-137925000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-1339000</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
+        <v>-321688000</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
       <c r="Y3" t="n">
-        <v>3317000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>60941000</v>
+        <v>-9357000</v>
       </c>
       <c r="AA3" t="n">
-        <v>60941000</v>
+        <v>8654000</v>
       </c>
       <c r="AB3" t="n">
+        <v>-18011000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-30535000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>38528000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-69063000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-190793000</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0</v>
       </c>
-      <c r="AC3" t="n">
-        <v>2811000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11811000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-9000000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-97868000</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-97868000</v>
+        <v>-190793000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-31912000</v>
+        <v>-30599000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78000</v>
+        <v>495000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-31990000</v>
+        <v>-31094000</v>
       </c>
       <c r="AL3" t="n">
-        <v>252960000</v>
+        <v>93921000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-71000</v>
+        <v>167000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-18466000</v>
+        <v>417155000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1126000</v>
+        <v>3291000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-9321000</v>
+        <v>-57132000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-190365000</v>
+        <v>518052000</v>
       </c>
       <c r="AR3" t="n">
-        <v>2378000</v>
+        <v>-9357000</v>
       </c>
       <c r="AS3" t="n">
-        <v>177716000</v>
+        <v>-37699000</v>
       </c>
       <c r="AT3" t="n">
-        <v>284703000</v>
+        <v>185261000</v>
       </c>
       <c r="AU3" t="n">
-        <v>10508000</v>
+        <v>13637000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-13527000</v>
+        <v>12859000</v>
       </c>
       <c r="AW3" t="n">
-        <v>117767000</v>
+        <v>250839000</v>
       </c>
       <c r="AX3" t="n">
-        <v>102224000</v>
+        <v>211366000</v>
       </c>
       <c r="AY3" t="n">
-        <v>15543000</v>
+        <v>39473000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>24539000</v>
+        <v>83033000</v>
       </c>
       <c r="BA3" t="n">
-        <v>22262000</v>
+        <v>52445000</v>
       </c>
       <c r="BB3" t="n">
-        <v>953000</v>
+        <v>1127000</v>
       </c>
       <c r="BC3" t="n">
-        <v>83519000</v>
+        <v>-16352000</v>
       </c>
       <c r="BD3" t="n">
-        <v>-560818000</v>
+        <v>-2589917000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-127966000</v>
+        <v>123102000</v>
       </c>
       <c r="C4" t="n">
-        <v>-33191000</v>
+        <v>-3184000</v>
       </c>
       <c r="D4" t="n">
-        <v>-1002816000</v>
+        <v>-2022209000</v>
       </c>
       <c r="E4" t="n">
-        <v>636700000</v>
+        <v>1602662000</v>
       </c>
       <c r="F4" t="n">
-        <v>159062000</v>
+        <v>456916000</v>
       </c>
       <c r="G4" t="n">
-        <v>-221887000</v>
+        <v>-129858000</v>
       </c>
       <c r="H4" t="n">
+        <v>190429000</v>
+      </c>
+      <c r="I4" t="n">
         <v>90527000</v>
       </c>
-      <c r="I4" t="n">
-        <v>714801000</v>
-      </c>
       <c r="J4" t="n">
-        <v>9651000</v>
+        <v>2982000</v>
       </c>
       <c r="K4" t="n">
-        <v>-633925000</v>
+        <v>96920000</v>
       </c>
       <c r="L4" t="n">
-        <v>-406158000</v>
+        <v>-18115000</v>
       </c>
       <c r="M4" t="n">
-        <v>-57231000</v>
+        <v>38050000</v>
       </c>
       <c r="N4" t="n">
-        <v>-78164000</v>
+        <v>-77542000</v>
       </c>
       <c r="O4" t="n">
-        <v>125871000</v>
+        <v>453732000</v>
       </c>
       <c r="P4" t="n">
-        <v>-33191000</v>
+        <v>-3184000</v>
       </c>
       <c r="Q4" t="n">
-        <v>159062000</v>
+        <v>456916000</v>
       </c>
       <c r="R4" t="n">
-        <v>-366116000</v>
+        <v>-419547000</v>
       </c>
       <c r="S4" t="n">
-        <v>-366116000</v>
+        <v>-419547000</v>
       </c>
       <c r="T4" t="n">
-        <v>-1002816000</v>
+        <v>-2022209000</v>
       </c>
       <c r="U4" t="n">
-        <v>636700000</v>
+        <v>1602662000</v>
       </c>
       <c r="V4" t="n">
-        <v>-321688000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="n">
+        <v>-137925000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-1339000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>3317000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>60941000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>60941000</v>
+      </c>
+      <c r="AB4" t="n">
         <v>0</v>
       </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-9357000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>8654000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-18011000</v>
-      </c>
       <c r="AC4" t="n">
-        <v>-30535000</v>
+        <v>2811000</v>
       </c>
       <c r="AD4" t="n">
-        <v>38528000</v>
+        <v>11811000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-69063000</v>
+        <v>-9000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-190793000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
+        <v>-97868000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-190793000</v>
+        <v>-97868000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-30599000</v>
+        <v>-31912000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>495000</v>
+        <v>78000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-31094000</v>
+        <v>-31990000</v>
       </c>
       <c r="AL4" t="n">
-        <v>93921000</v>
+        <v>252960000</v>
       </c>
       <c r="AM4" t="n">
-        <v>167000</v>
+        <v>-71000</v>
       </c>
       <c r="AN4" t="n">
-        <v>417155000</v>
+        <v>-18466000</v>
       </c>
       <c r="AO4" t="n">
-        <v>3291000</v>
+        <v>1126000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-57132000</v>
+        <v>-9321000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>518052000</v>
+        <v>-190365000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-9357000</v>
+        <v>2378000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-37699000</v>
+        <v>177716000</v>
       </c>
       <c r="AT4" t="n">
-        <v>185261000</v>
+        <v>284703000</v>
       </c>
       <c r="AU4" t="n">
-        <v>13637000</v>
+        <v>10508000</v>
       </c>
       <c r="AV4" t="n">
-        <v>12859000</v>
+        <v>-13527000</v>
       </c>
       <c r="AW4" t="n">
-        <v>250839000</v>
+        <v>117767000</v>
       </c>
       <c r="AX4" t="n">
-        <v>211366000</v>
+        <v>102224000</v>
       </c>
       <c r="AY4" t="n">
-        <v>39473000</v>
+        <v>15543000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>83033000</v>
+        <v>24539000</v>
       </c>
       <c r="BA4" t="n">
-        <v>52445000</v>
+        <v>22262000</v>
       </c>
       <c r="BB4" t="n">
-        <v>1127000</v>
+        <v>953000</v>
       </c>
       <c r="BC4" t="n">
-        <v>-16352000</v>
+        <v>83519000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-2589917000</v>
+        <v>-560818000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-112838000</v>
+        <v>-119312000</v>
       </c>
       <c r="C5" t="n">
-        <v>-5151000</v>
+        <v>-10051000</v>
       </c>
       <c r="D5" t="n">
-        <v>-855339000</v>
+        <v>-1080341000</v>
       </c>
       <c r="E5" t="n">
-        <v>713000000</v>
+        <v>1188738000</v>
       </c>
       <c r="F5" t="n">
-        <v>349230000</v>
+        <v>232571000</v>
       </c>
       <c r="G5" t="n">
-        <v>-266607000</v>
+        <v>-270988000</v>
       </c>
       <c r="H5" t="n">
-        <v>714801000</v>
+        <v>196926000</v>
       </c>
       <c r="I5" t="n">
-        <v>735567000</v>
+        <v>190429000</v>
       </c>
       <c r="J5" t="n">
-        <v>-18765000</v>
+        <v>-55000</v>
       </c>
       <c r="K5" t="n">
-        <v>-2001000</v>
+        <v>6552000</v>
       </c>
       <c r="L5" t="n">
-        <v>118985000</v>
+        <v>217060000</v>
       </c>
       <c r="M5" t="n">
-        <v>45815000</v>
+        <v>-27667000</v>
       </c>
       <c r="N5" t="n">
-        <v>-112461000</v>
+        <v>-73481000</v>
       </c>
       <c r="O5" t="n">
-        <v>344079000</v>
+        <v>222520000</v>
       </c>
       <c r="P5" t="n">
-        <v>-5151000</v>
+        <v>-10051000</v>
       </c>
       <c r="Q5" t="n">
-        <v>349230000</v>
+        <v>232571000</v>
       </c>
       <c r="R5" t="n">
-        <v>-142339000</v>
+        <v>108397000</v>
       </c>
       <c r="S5" t="n">
-        <v>-142339000</v>
+        <v>108397000</v>
       </c>
       <c r="T5" t="n">
-        <v>-855339000</v>
+        <v>-1080341000</v>
       </c>
       <c r="U5" t="n">
-        <v>713000000</v>
+        <v>1188738000</v>
       </c>
       <c r="V5" t="n">
-        <v>-274755000</v>
+        <v>-362184000</v>
       </c>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="n">
-        <v>9000</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
       <c r="Z5" t="n">
-        <v>48054000</v>
+        <v>-2155000</v>
       </c>
       <c r="AA5" t="n">
-        <v>58066000</v>
+        <v>845000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-10012000</v>
+        <v>-3000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-110173000</v>
+        <v>22500000</v>
       </c>
       <c r="AD5" t="n">
-        <v>7117000</v>
+        <v>22500000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-117290000</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-205167000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>21300000</v>
-      </c>
+        <v>-255777000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-226467000</v>
+        <v>-255777000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-39818000</v>
+        <v>-15211000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>322000</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-40140000</v>
+        <v>-15211000</v>
       </c>
       <c r="AL5" t="n">
-        <v>153769000</v>
+        <v>151676000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-11964000</v>
+        <v>-3273000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-226958000</v>
+        <v>79070000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-83000</v>
+        <v>-201000</v>
       </c>
       <c r="AP5" t="n">
-        <v>31587000</v>
+        <v>-64544000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-160982000</v>
+        <v>312010000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-11331000</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-86149000</v>
+        <v>-168195000</v>
       </c>
       <c r="AT5" t="n">
-        <v>220069000</v>
+        <v>129148000</v>
       </c>
       <c r="AU5" t="n">
-        <v>24894000</v>
+        <v>15569000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-25250000</v>
+        <v>-29513000</v>
       </c>
       <c r="AW5" t="n">
-        <v>233335000</v>
+        <v>73699000</v>
       </c>
       <c r="AX5" t="n">
-        <v>207247000</v>
+        <v>59983000</v>
       </c>
       <c r="AY5" t="n">
-        <v>26088000</v>
+        <v>13716000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1903000</v>
+        <v>81400000</v>
       </c>
       <c r="BA5" t="n">
-        <v>-59147000</v>
+        <v>5811000</v>
       </c>
       <c r="BB5" t="n">
-        <v>4806000</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-9354000</v>
+        <v>-6669000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-155930000</v>
+        <v>-544604000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-106590000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-24393000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1145108000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1090920000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>126169000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-173855000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>187907000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>196926000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-9018000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>14858000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>33937000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-55209000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>101776000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-24393000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>126169000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-54188000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-54188000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1145108000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1090920000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-91141000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-5000000</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>8034000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>8034000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>19146000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>19146000</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>-169271000</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>-169271000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-4478000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>106000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-4584000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>67265000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-3007000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-170244000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-123000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-23273000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-60310000</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>-86538000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>93053000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6687000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1177000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>67921000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>55443000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>12478000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>27909000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-12485000</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>-1078000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>19918000</v>
       </c>
     </row>
   </sheetData>
@@ -3447,7 +3645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ2"/>
+  <dimension ref="A1:EK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3603,550 +3801,555 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
+          <t>trailingPE</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>forwardPE</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bidSize</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>askSize</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>forwardEps</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4168,10 +4371,8 @@
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>518057</t>
-        </is>
+      <c r="D2" t="n">
+        <v>518057</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4228,7 +4429,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Xiangyu  Chen', 'age': 42, 'title': 'Co-founder, CEO &amp; Chairman of the Board', 'yearBorn': 1983, 'fiscalYear': 2025, 'totalPay': 2002427, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Song  Guan', 'age': 43, 'title': 'Founder, CTO &amp; Executive Director', 'yearBorn': 1982, 'fiscalYear': 2025, 'totalPay': 1642245, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jialiang  Yang', 'age': 42, 'title': 'Chief Human Resources Officer &amp; Executive Director', 'yearBorn': 1983, 'fiscalYear': 2025, 'totalPay': 1686254, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Junwen  Lei CPA', 'age': 42, 'title': 'Chief Financial Officer', 'yearBorn': 1983, 'fiscalYear': 2025, 'totalPay': 735420, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ho Kwan  Yau', 'age': 30, 'title': 'Chief Marketing Officer', 'yearBorn': 1995, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xu  Tang', 'age': 42, 'title': 'Joint Company Secretary', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ka Man  Ng A.C.I.S., A.C.S.', 'age': 47, 'title': 'Joint Company Secretary', 'yearBorn': 1978, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Xiangyu  Chen', 'age': 42, 'title': 'Co-founder, CEO &amp; Chairman of the Board', 'yearBorn': 1983, 'fiscalYear': 2025, 'totalPay': 2002630, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Song  Guan', 'age': 43, 'title': 'Founder, CTO &amp; Executive Director', 'yearBorn': 1982, 'fiscalYear': 2025, 'totalPay': 1642411, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jialiang  Yang', 'age': 42, 'title': 'Chief Human Resources Officer &amp; Executive Director', 'yearBorn': 1983, 'fiscalYear': 2025, 'totalPay': 1686425, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Junwen  Lei CPA', 'age': 42, 'title': 'Chief Financial Officer', 'yearBorn': 1983, 'fiscalYear': 2025, 'totalPay': 735494, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ho Kwan  Yau', 'age': 30, 'title': 'Chief Marketing Officer', 'yearBorn': 1995, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xu  Tang', 'age': 42, 'title': 'Joint Company Secretary', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ka Man  Ng A.C.I.S., A.C.S.', 'age': 47, 'title': 'Joint Company Secretary', 'yearBorn': 1978, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4246,407 +4447,410 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="V2" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="W2" t="n">
-        <v>0.335</v>
+        <v>0.32</v>
       </c>
       <c r="X2" t="n">
-        <v>0.355</v>
+        <v>0.34</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.335</v>
+        <v>0.32</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.355</v>
+        <v>0.34</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.555</v>
+        <v>0.49</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.8846154000000001</v>
+        <v>32.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>6285600</v>
+        <v>0.8333333000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>6285600</v>
+        <v>4662800</v>
       </c>
       <c r="AH2" t="n">
-        <v>3697856</v>
+        <v>4662800</v>
       </c>
       <c r="AI2" t="n">
-        <v>4952000</v>
+        <v>3646090</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4952000</v>
+        <v>4269960</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.345</v>
+        <v>4269960</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.35</v>
+        <v>0.325</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>704150400</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>714355482</v>
+        <v>663330048</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.335</v>
+        <v>663330091</v>
       </c>
       <c r="AR2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AS2" t="n">
         <v>1.35</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="AT2" t="n">
-        <v>0.35</v>
-      </c>
       <c r="AU2" t="n">
-        <v>0.5262359</v>
+        <v>0.32</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.434</v>
+        <v>0.49572942</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.6930500000000001</v>
+        <v>0.411</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>0.6396500000000001</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="inlineStr">
         <is>
           <t>HKD</t>
         </is>
       </c>
-      <c r="BA2" t="b">
+      <c r="BB2" t="b">
         <v>0</v>
       </c>
-      <c r="BB2" t="n">
-        <v>1913009408</v>
-      </c>
       <c r="BC2" t="n">
+        <v>1923214464</v>
+      </c>
+      <c r="BD2" t="n">
         <v>0.01191</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
         <v>1220527368</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BF2" t="n">
         <v>2041015665</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BG2" t="n">
         <v>0.40370998</v>
       </c>
-      <c r="BG2" t="n">
-        <v>0.0053600003</v>
-      </c>
       <c r="BH2" t="n">
+        <v>0.0054400004</v>
+      </c>
+      <c r="BI2" t="n">
         <v>2041015665</v>
       </c>
-      <c r="BI2" t="n">
-        <v>0.9496763</v>
-      </c>
       <c r="BJ2" t="n">
-        <v>0.3632817</v>
+        <v>0.94977224</v>
       </c>
       <c r="BK2" t="n">
+        <v>0.3421873</v>
+      </c>
+      <c r="BL2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BM2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BN2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BO2" t="n">
         <v>15940000</v>
       </c>
-      <c r="BO2" t="n">
-        <v>-0.27</v>
-      </c>
       <c r="BP2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>0.39</v>
       </c>
-      <c r="BQ2" t="n">
-        <v>1.43</v>
-      </c>
       <c r="BR2" t="n">
-        <v>17.261</v>
+        <v>1.437</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.520548</v>
+        <v>17.353</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
-      </c>
-      <c r="BU2" t="inlineStr">
+        <v>-0.59375</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.2568333</v>
+      </c>
+      <c r="BV2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="BV2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BW2" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BX2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="BX2" t="n">
+      <c r="BY2" t="n">
         <v>199336000</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="BZ2" t="n">
         <v>0.098</v>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CA2" t="n">
         <v>110826000</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CB2" t="n">
         <v>1322503936</v>
       </c>
-      <c r="CB2" t="n">
+      <c r="CC2" t="n">
         <v>0.374</v>
       </c>
-      <c r="CC2" t="n">
+      <c r="CD2" t="n">
         <v>0.961</v>
       </c>
-      <c r="CD2" t="n">
+      <c r="CE2" t="n">
         <v>1338088960</v>
       </c>
-      <c r="CE2" t="n">
+      <c r="CF2" t="n">
         <v>75.137</v>
       </c>
-      <c r="CF2" t="n">
+      <c r="CG2" t="n">
         <v>0.74</v>
       </c>
-      <c r="CG2" t="n">
+      <c r="CH2" t="n">
         <v>0.00945</v>
       </c>
-      <c r="CH2" t="n">
+      <c r="CI2" t="n">
         <v>0.01239</v>
       </c>
-      <c r="CI2" t="n">
+      <c r="CJ2" t="n">
         <v>532396000</v>
       </c>
-      <c r="CJ2" t="n">
+      <c r="CK2" t="n">
         <v>-164925744</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CL2" t="n">
         <v>67265000</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
         <v>-0.024</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
         <v>0.39788</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
         <v>0.08282</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>0.00283</v>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>1119.HK</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CV2" t="b">
+      <c r="CW2" t="b">
         <v>0</v>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>IDREAMSKY</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CY2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DA2" t="n">
+        <v>1781770086</v>
+      </c>
+      <c r="DB2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>finmb_590752068</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DD2" t="n">
+      <c r="DF2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DF2" t="b">
+      <c r="DH2" t="b">
         <v>0</v>
       </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>IDREAMSKY</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>iDreamSky Technology Holdings Limited</t>
-        </is>
-      </c>
       <c r="DI2" t="n">
-        <v>-1.4285702</v>
+        <v>-4.4117694</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+        <v>0.325</v>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
       </c>
       <c r="DL2" t="b">
         <v>0</v>
       </c>
-      <c r="DM2" t="b">
-        <v>0</v>
+      <c r="DM2" t="n">
+        <v>1544059800000</v>
       </c>
       <c r="DN2" t="n">
-        <v>1544059800000</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.004999995</v>
+        <v>-0.0150000155</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>0.32 - 0.34</t>
+        </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>0.335 - 0.355</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
           <t>HKSE</t>
         </is>
       </c>
+      <c r="DQ2" t="n">
+        <v>3646090</v>
+      </c>
       <c r="DR2" t="n">
-        <v>3697856</v>
+        <v>0.004999995</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.00999999</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.029850718</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>0.335 - 1.35</t>
-        </is>
+        <v>0.015624985</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>0.32 - 1.35</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>-1.0250001</v>
       </c>
       <c r="DV2" t="n">
-        <v>-1.005</v>
+        <v>-0.7592593399999999</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0.74444443</v>
+        <v>-59.375</v>
       </c>
       <c r="DX2" t="n">
-        <v>-52.0548</v>
+        <v>1743084553</v>
       </c>
       <c r="DY2" t="n">
         <v>1743084553</v>
       </c>
-      <c r="DZ2" t="n">
-        <v>1743084553</v>
-      </c>
-      <c r="EA2" t="b">
+      <c r="DZ2" t="b">
         <v>0</v>
       </c>
+      <c r="EA2" t="n">
+        <v>0.01</v>
+      </c>
       <c r="EB2" t="n">
-        <v>-0.27</v>
+        <v>0.39</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.39</v>
+        <v>-0.08600002499999999</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0.08899999</v>
+        <v>-0.2092458</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.2050691</v>
+        <v>-0.31465</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0.34805003</v>
+        <v>-0.49190965</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.5022004</v>
+        <v>15</v>
       </c>
       <c r="EH2" t="n">
         <v>15</v>
       </c>
-      <c r="EI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EJ2" t="inlineStr"/>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>iDreamSky Technology Holdings Limited</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
